--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/16.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/16.xlsx
@@ -426,13 +426,13 @@
         <v>-20.60095519089991</v>
       </c>
       <c r="E2">
-        <v>-53.42560138725172</v>
+        <v>-37.11766645142173</v>
       </c>
       <c r="F2">
-        <v>-9.672721287610113</v>
+        <v>-5.746054709721942</v>
       </c>
       <c r="G2">
-        <v>-33.22221120818645</v>
+        <v>-21.18895586313229</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-19.99341143202596</v>
       </c>
       <c r="E3">
-        <v>-53.0887202809916</v>
+        <v>-37.09832533893497</v>
       </c>
       <c r="F3">
-        <v>-9.551271632072808</v>
+        <v>-5.602901156466497</v>
       </c>
       <c r="G3">
-        <v>-33.47518654556986</v>
+        <v>-21.81821442760034</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-19.30246733831838</v>
       </c>
       <c r="E4">
-        <v>-53.60091786210317</v>
+        <v>-37.64188260254965</v>
       </c>
       <c r="F4">
-        <v>-9.470388603559485</v>
+        <v>-5.823294422776797</v>
       </c>
       <c r="G4">
-        <v>-33.31857870592548</v>
+        <v>-21.8532251019509</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-18.57128114002163</v>
       </c>
       <c r="E5">
-        <v>-53.44989098971035</v>
+        <v>-37.78127129674275</v>
       </c>
       <c r="F5">
-        <v>-9.523820861514016</v>
+        <v>-5.463782094030634</v>
       </c>
       <c r="G5">
-        <v>-33.54284747530149</v>
+        <v>-21.70432338468556</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-17.80849154913739</v>
       </c>
       <c r="E6">
-        <v>-53.38932491409477</v>
+        <v>-38.18479003014424</v>
       </c>
       <c r="F6">
-        <v>-9.482321827632321</v>
+        <v>-5.755605248245</v>
       </c>
       <c r="G6">
-        <v>-33.13773601766087</v>
+        <v>-21.63935227320459</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-17.04832523133097</v>
       </c>
       <c r="E7">
-        <v>-53.95057945413143</v>
+        <v>-37.75976783791733</v>
       </c>
       <c r="F7">
-        <v>-9.434773037153645</v>
+        <v>-5.743104265601478</v>
       </c>
       <c r="G7">
-        <v>-33.33094276587828</v>
+        <v>-21.04832388862405</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.32312375141424</v>
       </c>
       <c r="E8">
-        <v>-54.10865942479118</v>
+        <v>-39.42108834084528</v>
       </c>
       <c r="F8">
-        <v>-9.575100071276509</v>
+        <v>-5.404733618973474</v>
       </c>
       <c r="G8">
-        <v>-33.08269157697941</v>
+        <v>-21.16551554544148</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-15.66094361731613</v>
       </c>
       <c r="E9">
-        <v>-53.77821894068848</v>
+        <v>-37.61066783121478</v>
       </c>
       <c r="F9">
-        <v>-9.531656246530654</v>
+        <v>-5.477435222727638</v>
       </c>
       <c r="G9">
-        <v>-32.95605327846567</v>
+        <v>-21.81040981649151</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.0819333175007</v>
       </c>
       <c r="E10">
-        <v>-54.26832888982763</v>
+        <v>-38.9836196378083</v>
       </c>
       <c r="F10">
-        <v>-9.488992001021673</v>
+        <v>-5.549010811575924</v>
       </c>
       <c r="G10">
-        <v>-32.93350018697938</v>
+        <v>-20.0964758351728</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-14.60158135046036</v>
       </c>
       <c r="E11">
-        <v>-53.94709026490852</v>
+        <v>-39.27732740499778</v>
       </c>
       <c r="F11">
-        <v>-9.518802889320947</v>
+        <v>-5.400220057114472</v>
       </c>
       <c r="G11">
-        <v>-32.89172606809209</v>
+        <v>-20.56894199708265</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-14.22019013729912</v>
       </c>
       <c r="E12">
-        <v>-54.2820705442039</v>
+        <v>-39.18510503183158</v>
       </c>
       <c r="F12">
-        <v>-9.494394021899236</v>
+        <v>-5.469968049336341</v>
       </c>
       <c r="G12">
-        <v>-32.50640008586693</v>
+        <v>-20.39389359114815</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-13.93526220348142</v>
       </c>
       <c r="E13">
-        <v>-54.4467824650479</v>
+        <v>-40.50296342364777</v>
       </c>
       <c r="F13">
-        <v>-9.488265871859443</v>
+        <v>-5.504981411567834</v>
       </c>
       <c r="G13">
-        <v>-32.64539665087877</v>
+        <v>-20.17416937316118</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-13.74983974713855</v>
       </c>
       <c r="E14">
-        <v>-54.53831990652044</v>
+        <v>-40.73409900123627</v>
       </c>
       <c r="F14">
-        <v>-9.448282444538822</v>
+        <v>-5.484867554588795</v>
       </c>
       <c r="G14">
-        <v>-32.32599356197711</v>
+        <v>-20.59910272221818</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-13.64917289859406</v>
       </c>
       <c r="E15">
-        <v>-54.98832002925516</v>
+        <v>-41.32623546976824</v>
       </c>
       <c r="F15">
-        <v>-9.524560452176527</v>
+        <v>-5.70897857053559</v>
       </c>
       <c r="G15">
-        <v>-32.41530711480834</v>
+        <v>-19.35851881846832</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-13.6134533814571</v>
       </c>
       <c r="E16">
-        <v>-54.91377681861489</v>
+        <v>-42.09224496206171</v>
       </c>
       <c r="F16">
-        <v>-9.481716851972623</v>
+        <v>-5.264694423400742</v>
       </c>
       <c r="G16">
-        <v>-32.44508629957047</v>
+        <v>-19.44510448177519</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-13.62006911296388</v>
       </c>
       <c r="E17">
-        <v>-55.5464952069666</v>
+        <v>-42.11376427054616</v>
       </c>
       <c r="F17">
-        <v>-9.465580076473731</v>
+        <v>-5.187220321870401</v>
       </c>
       <c r="G17">
-        <v>-31.99252562035187</v>
+        <v>-19.56387030299654</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-13.64149086400834</v>
       </c>
       <c r="E18">
-        <v>-55.79399442538181</v>
+        <v>-42.06187927960327</v>
       </c>
       <c r="F18">
-        <v>-9.367464347968033</v>
+        <v>-5.004409980639395</v>
       </c>
       <c r="G18">
-        <v>-31.8696770688442</v>
+        <v>-18.7439607314674</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-13.65476310760857</v>
       </c>
       <c r="E19">
-        <v>-56.06232688846931</v>
+        <v>-41.51251198383675</v>
       </c>
       <c r="F19">
-        <v>-9.380676414567587</v>
+        <v>-5.252495136734112</v>
       </c>
       <c r="G19">
-        <v>-31.92419430514854</v>
+        <v>-18.34741531040965</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-13.64985779779838</v>
       </c>
       <c r="E20">
-        <v>-55.88893614718963</v>
+        <v>-42.93631402506239</v>
       </c>
       <c r="F20">
-        <v>-9.179984845771832</v>
+        <v>-4.861630181979994</v>
       </c>
       <c r="G20">
-        <v>-31.48184914182774</v>
+        <v>-18.04287160516101</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-13.61727130680927</v>
       </c>
       <c r="E21">
-        <v>-55.71618844921903</v>
+        <v>-43.86804075942956</v>
       </c>
       <c r="F21">
-        <v>-9.151062812417598</v>
+        <v>-4.709130388264583</v>
       </c>
       <c r="G21">
-        <v>-31.64189415537827</v>
+        <v>-17.80488972852497</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-13.54954263879827</v>
       </c>
       <c r="E22">
-        <v>-55.92365369316943</v>
+        <v>-43.04710314166005</v>
       </c>
       <c r="F22">
-        <v>-9.227928374949931</v>
+        <v>-4.207582602639276</v>
       </c>
       <c r="G22">
-        <v>-31.70050239833275</v>
+        <v>-17.62636524977423</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-13.44330311576611</v>
       </c>
       <c r="E23">
-        <v>-56.43492180499092</v>
+        <v>-42.98424339395958</v>
       </c>
       <c r="F23">
-        <v>-9.172766710135738</v>
+        <v>-4.726285882593581</v>
       </c>
       <c r="G23">
-        <v>-31.62069921519947</v>
+        <v>-18.10530518348613</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-13.29623607673533</v>
       </c>
       <c r="E24">
-        <v>-56.61734685191591</v>
+        <v>-44.76957842182459</v>
       </c>
       <c r="F24">
-        <v>-9.21280873457523</v>
+        <v>-4.319554570125634</v>
       </c>
       <c r="G24">
-        <v>-31.5790053770415</v>
+        <v>-17.60518106886843</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-13.1069603040636</v>
       </c>
       <c r="E25">
-        <v>-56.36071822990123</v>
+        <v>-44.00773512561818</v>
       </c>
       <c r="F25">
-        <v>-8.957461890931745</v>
+        <v>-4.236642022481674</v>
       </c>
       <c r="G25">
-        <v>-31.35005466863658</v>
+        <v>-17.99523451012367</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-12.88249099312275</v>
       </c>
       <c r="E26">
-        <v>-56.45796494497895</v>
+        <v>-45.0316570623075</v>
       </c>
       <c r="F26">
-        <v>-8.859036943846057</v>
+        <v>-4.825906527645427</v>
       </c>
       <c r="G26">
-        <v>-31.53668170759469</v>
+        <v>-18.09340873809076</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-12.63218088725692</v>
       </c>
       <c r="E27">
-        <v>-56.53370254063874</v>
+        <v>-44.17187193026319</v>
       </c>
       <c r="F27">
-        <v>-8.90691237366979</v>
+        <v>-4.527530790205931</v>
       </c>
       <c r="G27">
-        <v>-31.5897720987716</v>
+        <v>-18.02796421859768</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-12.36097735336157</v>
       </c>
       <c r="E28">
-        <v>-56.33266999401623</v>
+        <v>-44.76611866768273</v>
       </c>
       <c r="F28">
-        <v>-8.908071250473414</v>
+        <v>-4.213953851537089</v>
       </c>
       <c r="G28">
-        <v>-31.46515902649151</v>
+        <v>-17.63281253721196</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-12.07363045006309</v>
       </c>
       <c r="E29">
-        <v>-56.41349419810513</v>
+        <v>-43.86346700068181</v>
       </c>
       <c r="F29">
-        <v>-8.945296653942297</v>
+        <v>-4.236448810359991</v>
       </c>
       <c r="G29">
-        <v>-31.78522091395547</v>
+        <v>-17.59290556600882</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-11.7740724669846</v>
       </c>
       <c r="E30">
-        <v>-56.1799200372635</v>
+        <v>-44.29669931628462</v>
       </c>
       <c r="F30">
-        <v>-8.933017786053416</v>
+        <v>-4.227964897770982</v>
       </c>
       <c r="G30">
-        <v>-31.45249287925825</v>
+        <v>-18.17042526951636</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-11.46241307460461</v>
       </c>
       <c r="E31">
-        <v>-56.14401150261968</v>
+        <v>-45.13394396895576</v>
       </c>
       <c r="F31">
-        <v>-8.89923496331822</v>
+        <v>-4.297224316717937</v>
       </c>
       <c r="G31">
-        <v>-31.87120240270142</v>
+        <v>-17.97399901576202</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-11.1426179904555</v>
       </c>
       <c r="E32">
-        <v>-56.65826048245671</v>
+        <v>-43.82232128584812</v>
       </c>
       <c r="F32">
-        <v>-8.959695708125473</v>
+        <v>-4.468280392644552</v>
       </c>
       <c r="G32">
-        <v>-31.54226990846498</v>
+        <v>-18.22996543104016</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.82696893515175</v>
       </c>
       <c r="E33">
-        <v>-56.63698118309467</v>
+        <v>-43.23689375155852</v>
       </c>
       <c r="F33">
-        <v>-8.985708869639522</v>
+        <v>-4.330562118090896</v>
       </c>
       <c r="G33">
-        <v>-31.72222040470676</v>
+        <v>-18.81349046415594</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.52110426955442</v>
       </c>
       <c r="E34">
-        <v>-56.00763084728617</v>
+        <v>-42.32108913180232</v>
       </c>
       <c r="F34">
-        <v>-8.830259819583086</v>
+        <v>-4.148438313374232</v>
       </c>
       <c r="G34">
-        <v>-32.10447916648978</v>
+        <v>-19.10851966152471</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.23014634220114</v>
       </c>
       <c r="E35">
-        <v>-55.66165996157417</v>
+        <v>-42.54687658158776</v>
       </c>
       <c r="F35">
-        <v>-8.987589916340585</v>
+        <v>-4.050902617160063</v>
       </c>
       <c r="G35">
-        <v>-31.89289640762027</v>
+        <v>-18.42814792920309</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.958367218268766</v>
       </c>
       <c r="E36">
-        <v>-56.06278426434409</v>
+        <v>-43.10031497548718</v>
       </c>
       <c r="F36">
-        <v>-8.963101863623104</v>
+        <v>-4.320353549759973</v>
       </c>
       <c r="G36">
-        <v>-31.7102304363999</v>
+        <v>-19.12483237466947</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.705694331189187</v>
       </c>
       <c r="E37">
-        <v>-55.97593832194349</v>
+        <v>-43.02038061654078</v>
       </c>
       <c r="F37">
-        <v>-8.960641972409947</v>
+        <v>-3.840590430854493</v>
       </c>
       <c r="G37">
-        <v>-31.66911842662046</v>
+        <v>-18.81655768459808</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.473309369728106</v>
       </c>
       <c r="E38">
-        <v>-55.46554420560548</v>
+        <v>-42.24823277772992</v>
       </c>
       <c r="F38">
-        <v>-8.999119691331463</v>
+        <v>-3.824034369214489</v>
       </c>
       <c r="G38">
-        <v>-31.62814711502644</v>
+        <v>-18.57402877366384</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.269237453859491</v>
       </c>
       <c r="E39">
-        <v>-55.77628582777482</v>
+        <v>-42.46447194007018</v>
       </c>
       <c r="F39">
-        <v>-9.058241808713692</v>
+        <v>-4.226095332937805</v>
       </c>
       <c r="G39">
-        <v>-31.8193501555562</v>
+        <v>-19.39195367314219</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.09699897738391</v>
       </c>
       <c r="E40">
-        <v>-55.79807910893673</v>
+        <v>-40.81948111441389</v>
       </c>
       <c r="F40">
-        <v>-8.957073091129505</v>
+        <v>-4.127593576115218</v>
       </c>
       <c r="G40">
-        <v>-32.16158193886029</v>
+        <v>-19.14202734820045</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.957428486686675</v>
       </c>
       <c r="E41">
-        <v>-55.51808582527948</v>
+        <v>-40.64944823661089</v>
       </c>
       <c r="F41">
-        <v>-8.927231320564879</v>
+        <v>-4.127416992905647</v>
       </c>
       <c r="G41">
-        <v>-31.92651003175326</v>
+        <v>-18.69483223566462</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.850079510783264</v>
       </c>
       <c r="E42">
-        <v>-55.02088768219982</v>
+        <v>-40.61980710999368</v>
       </c>
       <c r="F42">
-        <v>-8.932643635530892</v>
+        <v>-3.871881292331746</v>
       </c>
       <c r="G42">
-        <v>-31.95012580835765</v>
+        <v>-19.65800732067849</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.771163402965602</v>
       </c>
       <c r="E43">
-        <v>-55.13750720908235</v>
+        <v>-39.8183079669021</v>
       </c>
       <c r="F43">
-        <v>-8.948669947542182</v>
+        <v>-4.118873691344809</v>
       </c>
       <c r="G43">
-        <v>-31.88100989386151</v>
+        <v>-19.38743974429939</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.715248281349327</v>
       </c>
       <c r="E44">
-        <v>-54.54553829408867</v>
+        <v>-40.84860825923123</v>
       </c>
       <c r="F44">
-        <v>-8.987905469744238</v>
+        <v>-4.191032083969976</v>
       </c>
       <c r="G44">
-        <v>-32.10577110688649</v>
+        <v>-19.99175996922011</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.682311433007957</v>
       </c>
       <c r="E45">
-        <v>-54.91591425834652</v>
+        <v>-39.58241522736854</v>
       </c>
       <c r="F45">
-        <v>-8.904366566410722</v>
+        <v>-4.201547891248494</v>
       </c>
       <c r="G45">
-        <v>-31.79401206763501</v>
+        <v>-19.92157474851479</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.672141975319043</v>
       </c>
       <c r="E46">
-        <v>-54.76220539722267</v>
+        <v>-38.84510720333568</v>
       </c>
       <c r="F46">
-        <v>-8.949046869550058</v>
+        <v>-4.116038857756172</v>
       </c>
       <c r="G46">
-        <v>-31.97477613044306</v>
+        <v>-19.78029556235363</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.680980194723041</v>
       </c>
       <c r="E47">
-        <v>-54.20949382340147</v>
+        <v>-38.86928925453664</v>
       </c>
       <c r="F47">
-        <v>-8.987842121507621</v>
+        <v>-4.134088354074436</v>
       </c>
       <c r="G47">
-        <v>-31.86279858284998</v>
+        <v>-19.81879058588427</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.70471224856135</v>
       </c>
       <c r="E48">
-        <v>-54.00927300574484</v>
+        <v>-38.65348708993812</v>
       </c>
       <c r="F48">
-        <v>-9.097277783970402</v>
+        <v>-3.933380552293048</v>
       </c>
       <c r="G48">
-        <v>-31.56914905533471</v>
+        <v>-19.53003156176688</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.738390302292572</v>
       </c>
       <c r="E49">
-        <v>-54.00603061835535</v>
+        <v>-39.04692770443553</v>
       </c>
       <c r="F49">
-        <v>-9.04592136854453</v>
+        <v>-3.849478188451939</v>
       </c>
       <c r="G49">
-        <v>-32.13334133013753</v>
+        <v>-19.47730284769014</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.774163042710716</v>
       </c>
       <c r="E50">
-        <v>-54.27352984222544</v>
+        <v>-36.80554364468006</v>
       </c>
       <c r="F50">
-        <v>-9.027588388867404</v>
+        <v>-4.274504471655043</v>
       </c>
       <c r="G50">
-        <v>-32.3043574916052</v>
+        <v>-19.80992825547564</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.809674443848618</v>
       </c>
       <c r="E51">
-        <v>-53.76835026370726</v>
+        <v>-37.57548611664919</v>
       </c>
       <c r="F51">
-        <v>-9.113492556985628</v>
+        <v>-3.868724966442275</v>
       </c>
       <c r="G51">
-        <v>-32.01386539689801</v>
+        <v>-19.85445012716053</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.846650289025206</v>
       </c>
       <c r="E52">
-        <v>-53.83877143088205</v>
+        <v>-37.72643600498387</v>
       </c>
       <c r="F52">
-        <v>-8.926573290757014</v>
+        <v>-3.874725628155875</v>
       </c>
       <c r="G52">
-        <v>-31.86551405782857</v>
+        <v>-19.97013217521205</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.882988546666937</v>
       </c>
       <c r="E53">
-        <v>-53.74146810987923</v>
+        <v>-36.72833316284927</v>
       </c>
       <c r="F53">
-        <v>-9.138338131313521</v>
+        <v>-3.7982429265286</v>
       </c>
       <c r="G53">
-        <v>-32.19927994855235</v>
+        <v>-20.0185538695422</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.916928836791461</v>
       </c>
       <c r="E54">
-        <v>-53.28036077252221</v>
+        <v>-36.14960324161702</v>
       </c>
       <c r="F54">
-        <v>-9.134881297226595</v>
+        <v>-4.168771513622559</v>
       </c>
       <c r="G54">
-        <v>-32.09546620625912</v>
+        <v>-19.64669684184356</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.947015337687807</v>
       </c>
       <c r="E55">
-        <v>-52.9963258258131</v>
+        <v>-35.23258951930078</v>
       </c>
       <c r="F55">
-        <v>-9.100517254420433</v>
+        <v>-4.406993349275918</v>
       </c>
       <c r="G55">
-        <v>-32.02506993827567</v>
+        <v>-19.91432299851102</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.968271634586218</v>
       </c>
       <c r="E56">
-        <v>-53.27253783367395</v>
+        <v>-35.75524787537006</v>
       </c>
       <c r="F56">
-        <v>-9.103532630483429</v>
+        <v>-4.054127834256855</v>
       </c>
       <c r="G56">
-        <v>-31.87332611766487</v>
+        <v>-19.99146202012158</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.979911000632752</v>
       </c>
       <c r="E57">
-        <v>-52.93631788461897</v>
+        <v>-35.66297116051576</v>
       </c>
       <c r="F57">
-        <v>-9.302265550988263</v>
+        <v>-4.083437479633893</v>
       </c>
       <c r="G57">
-        <v>-32.03497509052917</v>
+        <v>-20.47350062445824</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.986494598194053</v>
       </c>
       <c r="E58">
-        <v>-53.0237751710106</v>
+        <v>-35.18943089777068</v>
       </c>
       <c r="F58">
-        <v>-9.200419007272268</v>
+        <v>-4.172742656205524</v>
       </c>
       <c r="G58">
-        <v>-32.155066785239</v>
+        <v>-20.1815005762579</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.989764310801903</v>
       </c>
       <c r="E59">
-        <v>-52.83824019456084</v>
+        <v>-35.23294274027337</v>
       </c>
       <c r="F59">
-        <v>-9.138955776620541</v>
+        <v>-4.448784972825493</v>
       </c>
       <c r="G59">
-        <v>-32.42056674403386</v>
+        <v>-19.60355712292132</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.990701435922215</v>
       </c>
       <c r="E60">
-        <v>-52.76279694971155</v>
+        <v>-34.49635247937074</v>
       </c>
       <c r="F60">
-        <v>-9.097908890777704</v>
+        <v>-4.580503377518506</v>
       </c>
       <c r="G60">
-        <v>-32.36689866266035</v>
+        <v>-20.51736866339912</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.989900725772905</v>
       </c>
       <c r="E61">
-        <v>-52.04502929102179</v>
+        <v>-34.52636041238257</v>
       </c>
       <c r="F61">
-        <v>-9.369215134857551</v>
+        <v>-4.394604017899436</v>
       </c>
       <c r="G61">
-        <v>-32.31797459304461</v>
+        <v>-20.10539775540113</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.984995941052679</v>
       </c>
       <c r="E62">
-        <v>-52.61585249663666</v>
+        <v>-33.5301617935682</v>
       </c>
       <c r="F62">
-        <v>-9.477141525582919</v>
+        <v>-4.696338003732621</v>
       </c>
       <c r="G62">
-        <v>-32.33937478704684</v>
+        <v>-20.54290952223459</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.973636166133364</v>
       </c>
       <c r="E63">
-        <v>-52.27939367057776</v>
+        <v>-33.77778554501862</v>
       </c>
       <c r="F63">
-        <v>-9.265010848959944</v>
+        <v>-4.707348719109714</v>
       </c>
       <c r="G63">
-        <v>-32.35710193077326</v>
+        <v>-20.43957415377178</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.958887487239222</v>
       </c>
       <c r="E64">
-        <v>-52.05172690407914</v>
+        <v>-34.27787625087068</v>
       </c>
       <c r="F64">
-        <v>-9.166705867597351</v>
+        <v>-4.830212624029507</v>
       </c>
       <c r="G64">
-        <v>-32.5538120638076</v>
+        <v>-20.379739353695</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.943496635086841</v>
       </c>
       <c r="E65">
-        <v>-52.34459124298469</v>
+        <v>-33.98780937678336</v>
       </c>
       <c r="F65">
-        <v>-9.325000045330876</v>
+        <v>-4.546218520008116</v>
       </c>
       <c r="G65">
-        <v>-32.04564911698417</v>
+        <v>-20.71506451136777</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.927990771748812</v>
       </c>
       <c r="E66">
-        <v>-52.50140663727781</v>
+        <v>-33.7176745810408</v>
       </c>
       <c r="F66">
-        <v>-9.120845307624535</v>
+        <v>-4.585549064565097</v>
       </c>
       <c r="G66">
-        <v>-32.3241462775662</v>
+        <v>-20.14011213592593</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.912861134644706</v>
       </c>
       <c r="E67">
-        <v>-51.99064458242668</v>
+        <v>-34.15278394911979</v>
       </c>
       <c r="F67">
-        <v>-9.305710903207302</v>
+        <v>-4.796704574270638</v>
       </c>
       <c r="G67">
-        <v>-32.41075345941907</v>
+        <v>-20.52674247309356</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.89742846151486</v>
       </c>
       <c r="E68">
-        <v>-52.02095365896001</v>
+        <v>-33.07543281185097</v>
       </c>
       <c r="F68">
-        <v>-9.366475719550319</v>
+        <v>-5.039900830204394</v>
       </c>
       <c r="G68">
-        <v>-32.39563916375953</v>
+        <v>-19.78268412096021</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.878603992142866</v>
       </c>
       <c r="E69">
-        <v>-52.43125038583248</v>
+        <v>-33.89987094002841</v>
       </c>
       <c r="F69">
-        <v>-9.328720170526243</v>
+        <v>-5.303428702680559</v>
       </c>
       <c r="G69">
-        <v>-32.37358017119498</v>
+        <v>-20.45600439128319</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.858343663383589</v>
       </c>
       <c r="E70">
-        <v>-52.3083476012643</v>
+        <v>-33.66257210931547</v>
       </c>
       <c r="F70">
-        <v>-9.451951099291938</v>
+        <v>-5.088290172597688</v>
       </c>
       <c r="G70">
-        <v>-32.14955389927973</v>
+        <v>-20.2383310562578</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.841538475497201</v>
       </c>
       <c r="E71">
-        <v>-52.40724834147332</v>
+        <v>-33.94765539775735</v>
       </c>
       <c r="F71">
-        <v>-9.497108493838299</v>
+        <v>-5.13586786570932</v>
       </c>
       <c r="G71">
-        <v>-32.33351346616956</v>
+        <v>-19.99357414817563</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.828947553921825</v>
       </c>
       <c r="E72">
-        <v>-51.35266976787057</v>
+        <v>-32.33704927524129</v>
       </c>
       <c r="F72">
-        <v>-9.496925575805067</v>
+        <v>-5.271874946021344</v>
       </c>
       <c r="G72">
-        <v>-32.2748605308503</v>
+        <v>-20.02270529364845</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.820843190694267</v>
       </c>
       <c r="E73">
-        <v>-52.09822980366391</v>
+        <v>-34.1567395711655</v>
       </c>
       <c r="F73">
-        <v>-9.456400521061365</v>
+        <v>-5.112025173152379</v>
       </c>
       <c r="G73">
-        <v>-32.42570305543803</v>
+        <v>-20.06121521463402</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.816808442165073</v>
       </c>
       <c r="E74">
-        <v>-52.41694380432374</v>
+        <v>-34.37356064241575</v>
       </c>
       <c r="F74">
-        <v>-9.389584364415454</v>
+        <v>-5.539407218904699</v>
       </c>
       <c r="G74">
-        <v>-32.18394219106891</v>
+        <v>-19.29814771001417</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.811735621037627</v>
       </c>
       <c r="E75">
-        <v>-52.49261573711042</v>
+        <v>-34.04618140674224</v>
       </c>
       <c r="F75">
-        <v>-9.540894003135412</v>
+        <v>-5.23764314265912</v>
       </c>
       <c r="G75">
-        <v>-32.22454851501723</v>
+        <v>-19.80862390053317</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.8043290902436</v>
       </c>
       <c r="E76">
-        <v>-52.4124289157381</v>
+        <v>-34.78277619611888</v>
       </c>
       <c r="F76">
-        <v>-9.507160671210073</v>
+        <v>-5.282048672822127</v>
       </c>
       <c r="G76">
-        <v>-31.94034976738018</v>
+        <v>-19.3248737441527</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.797611383279275</v>
       </c>
       <c r="E77">
-        <v>-52.99605638160965</v>
+        <v>-33.88608852938606</v>
       </c>
       <c r="F77">
-        <v>-9.412667274059462</v>
+        <v>-5.083877176064315</v>
       </c>
       <c r="G77">
-        <v>-32.01932614176503</v>
+        <v>-19.63638614776151</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.790566602625807</v>
       </c>
       <c r="E78">
-        <v>-52.50912315698688</v>
+        <v>-34.05918265561825</v>
       </c>
       <c r="F78">
-        <v>-9.623345692357978</v>
+        <v>-5.699283122921269</v>
       </c>
       <c r="G78">
-        <v>-31.85046928362535</v>
+        <v>-19.31304516494089</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.781026931871134</v>
       </c>
       <c r="E79">
-        <v>-52.99796060492987</v>
+        <v>-35.31358127692796</v>
       </c>
       <c r="F79">
-        <v>-9.733069985223848</v>
+        <v>-5.952939756426501</v>
       </c>
       <c r="G79">
-        <v>-32.17672933997522</v>
+        <v>-19.43312196219579</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.766309502662219</v>
       </c>
       <c r="E80">
-        <v>-52.95955235263382</v>
+        <v>-35.22317029336482</v>
       </c>
       <c r="F80">
-        <v>-9.629796522478042</v>
+        <v>-5.399385444097035</v>
       </c>
       <c r="G80">
-        <v>-31.54137275062384</v>
+        <v>-19.57359171997261</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.741164394145994</v>
       </c>
       <c r="E81">
-        <v>-53.22982526683361</v>
+        <v>-36.25404343765592</v>
       </c>
       <c r="F81">
-        <v>-9.677041241420953</v>
+        <v>-5.58320698155505</v>
       </c>
       <c r="G81">
-        <v>-31.7020533889179</v>
+        <v>-19.00162876715273</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.701057231906507</v>
       </c>
       <c r="E82">
-        <v>-53.18135474529251</v>
+        <v>-36.14120065809579</v>
       </c>
       <c r="F82">
-        <v>-9.603080393500775</v>
+        <v>-5.993493713803159</v>
       </c>
       <c r="G82">
-        <v>-31.97361743950432</v>
+        <v>-18.48859021438633</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.646909054910026</v>
       </c>
       <c r="E83">
-        <v>-53.55018310355823</v>
+        <v>-35.85472259965955</v>
       </c>
       <c r="F83">
-        <v>-9.632294818559648</v>
+        <v>-5.818051564343735</v>
       </c>
       <c r="G83">
-        <v>-31.97122225980666</v>
+        <v>-18.6853044856026</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.578986272553637</v>
       </c>
       <c r="E84">
-        <v>-53.62069597233167</v>
+        <v>-38.20248957080322</v>
       </c>
       <c r="F84">
-        <v>-9.597407756874912</v>
+        <v>-5.856120687139068</v>
       </c>
       <c r="G84">
-        <v>-31.73630346543082</v>
+        <v>-18.6372121905536</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.495750432203085</v>
       </c>
       <c r="E85">
-        <v>-54.22059650954978</v>
+        <v>-37.34602833868053</v>
       </c>
       <c r="F85">
-        <v>-9.548182613684743</v>
+        <v>-5.380683460941611</v>
       </c>
       <c r="G85">
-        <v>-31.69786720408349</v>
+        <v>-18.59492990292603</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.395488718554805</v>
       </c>
       <c r="E86">
-        <v>-54.54904446508911</v>
+        <v>-38.75309540421083</v>
       </c>
       <c r="F86">
-        <v>-9.635215172267719</v>
+        <v>-6.047925686116812</v>
       </c>
       <c r="G86">
-        <v>-31.79082566755346</v>
+        <v>-18.77532318463369</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.275696365331056</v>
       </c>
       <c r="E87">
-        <v>-54.74981888869318</v>
+        <v>-38.2847810004706</v>
       </c>
       <c r="F87">
-        <v>-9.537148538645397</v>
+        <v>-5.693157348440349</v>
       </c>
       <c r="G87">
-        <v>-31.40548064969145</v>
+        <v>-19.15363412086113</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.132652488663355</v>
       </c>
       <c r="E88">
-        <v>-55.22659701035375</v>
+        <v>-39.43678176751887</v>
       </c>
       <c r="F88">
-        <v>-9.682063964731769</v>
+        <v>-5.573520244323265</v>
       </c>
       <c r="G88">
-        <v>-31.4994811073699</v>
+        <v>-18.45398177131879</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.966815997760618</v>
       </c>
       <c r="E89">
-        <v>-55.33905713386024</v>
+        <v>-40.63952861429708</v>
       </c>
       <c r="F89">
-        <v>-9.658191973615393</v>
+        <v>-5.644051379120318</v>
       </c>
       <c r="G89">
-        <v>-31.27252665792516</v>
+        <v>-18.17499878817887</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.781850960935778</v>
       </c>
       <c r="E90">
-        <v>-55.88452428138766</v>
+        <v>-41.56644837350511</v>
       </c>
       <c r="F90">
-        <v>-9.632652736096537</v>
+        <v>-5.83729834233407</v>
       </c>
       <c r="G90">
-        <v>-31.6797684516203</v>
+        <v>-18.64748977918027</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.578465579616061</v>
       </c>
       <c r="E91">
-        <v>-56.04251028621175</v>
+        <v>-41.78744469779043</v>
       </c>
       <c r="F91">
-        <v>-9.578920365871028</v>
+        <v>-6.187003176272396</v>
       </c>
       <c r="G91">
-        <v>-31.56114912203906</v>
+        <v>-18.47575026351227</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.357510072595361</v>
       </c>
       <c r="E92">
-        <v>-56.74494226767453</v>
+        <v>-43.66922716507081</v>
       </c>
       <c r="F92">
-        <v>-9.776413838533792</v>
+        <v>-5.887564376237161</v>
       </c>
       <c r="G92">
-        <v>-31.98378246958265</v>
+        <v>-17.95327996650449</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.120034227891022</v>
       </c>
       <c r="E93">
-        <v>-57.22190039617691</v>
+        <v>-44.49553781725042</v>
       </c>
       <c r="F93">
-        <v>-9.648773080646556</v>
+        <v>-6.109349324120653</v>
       </c>
       <c r="G93">
-        <v>-31.64417263834567</v>
+        <v>-19.14303375404439</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.865042256210759</v>
       </c>
       <c r="E94">
-        <v>-57.41344012916084</v>
+        <v>-45.57059528243435</v>
       </c>
       <c r="F94">
-        <v>-9.766591892409476</v>
+        <v>-5.850413802872782</v>
       </c>
       <c r="G94">
-        <v>-31.61893386679065</v>
+        <v>-18.56577061781613</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.593273661571645</v>
       </c>
       <c r="E95">
-        <v>-58.43381853493916</v>
+        <v>-45.97695336903865</v>
       </c>
       <c r="F95">
-        <v>-9.588240871109869</v>
+        <v>-6.352983870666505</v>
       </c>
       <c r="G95">
-        <v>-31.56329021736658</v>
+        <v>-18.71135682372389</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.31054758111159</v>
       </c>
       <c r="E96">
-        <v>-58.59543694197666</v>
+        <v>-48.00032536887985</v>
       </c>
       <c r="F96">
-        <v>-9.690028817706994</v>
+        <v>-6.276965590798933</v>
       </c>
       <c r="G96">
-        <v>-31.51572512669472</v>
+        <v>-19.95363572678986</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.02042324927025</v>
       </c>
       <c r="E97">
-        <v>-59.3324358976585</v>
+        <v>-48.89063581209136</v>
       </c>
       <c r="F97">
-        <v>-9.542498693154231</v>
+        <v>-6.442633503274744</v>
       </c>
       <c r="G97">
-        <v>-31.89854337067388</v>
+        <v>-18.39327795303794</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.723526082165724</v>
       </c>
       <c r="E98">
-        <v>-59.31473579094027</v>
+        <v>-50.42916787441984</v>
       </c>
       <c r="F98">
-        <v>-9.643401348144625</v>
+        <v>-6.096038275901384</v>
       </c>
       <c r="G98">
-        <v>-31.70390398387435</v>
+        <v>-18.8883402435261</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.42512495640701</v>
       </c>
       <c r="E99">
-        <v>-60.80787556193436</v>
+        <v>-52.2559791957211</v>
       </c>
       <c r="F99">
-        <v>-9.784574477152812</v>
+        <v>-6.467979924598395</v>
       </c>
       <c r="G99">
-        <v>-31.88910417770503</v>
+        <v>-19.33822186376705</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.122780925028946</v>
       </c>
       <c r="E100">
-        <v>-60.60057956969999</v>
+        <v>-52.77039572909642</v>
       </c>
       <c r="F100">
-        <v>-9.721575051763111</v>
+        <v>-6.366498425095908</v>
       </c>
       <c r="G100">
-        <v>-31.99031500356802</v>
+        <v>-19.44283510280802</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.82512137949957</v>
       </c>
       <c r="E101">
-        <v>-61.72524193916395</v>
+        <v>-54.96517613072046</v>
       </c>
       <c r="F101">
-        <v>-9.599095987380769</v>
+        <v>-6.237519831636604</v>
       </c>
       <c r="G101">
-        <v>-32.06759306809123</v>
+        <v>-19.53964207546738</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.52735006188713</v>
       </c>
       <c r="E102">
-        <v>-62.54823095565893</v>
+        <v>-55.15192473820427</v>
       </c>
       <c r="F102">
-        <v>-9.572529914538991</v>
+        <v>-6.498390245586663</v>
       </c>
       <c r="G102">
-        <v>-31.74028522407817</v>
+        <v>-19.35793781772617</v>
       </c>
     </row>
   </sheetData>
